--- a/artfynd/A 22467-2024 artfynd.xlsx
+++ b/artfynd/A 22467-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118745238</v>
+        <v>118753687</v>
       </c>
       <c r="B2" t="n">
         <v>57290</v>
@@ -711,25 +711,21 @@
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Aronsjö, Ås lm</t>
+          <t>aronsjö, Aronsjö, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581156</v>
+        <v>581127</v>
       </c>
       <c r="R2" t="n">
-        <v>7179772</v>
+        <v>7179756</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,19 +769,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>johan åslund</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Isak Vahlström</t>
+          <t>johan åslund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118753687</v>
+        <v>118745238</v>
       </c>
       <c r="B3" t="n">
         <v>57290</v>
@@ -821,21 +817,25 @@
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>aronsjö, Aronsjö, Ås lm</t>
+          <t>Aronsjö, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581127</v>
+        <v>581156</v>
       </c>
       <c r="R3" t="n">
-        <v>7179756</v>
+        <v>7179772</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,12 +879,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>johan åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>johan åslund</t>
+          <t>Via Isak Vahlström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
